--- a/Project-FTO/Rol_Operadores.xlsx
+++ b/Project-FTO/Rol_Operadores.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jtinoco2\Downloads\Failures-PMI\Project-FTO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Francisco\Downloads\Failures-PMI\Project-FTO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ECABA4F3-18EB-49DA-993E-EFC877B113A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35493B68-F8F6-4D47-8C22-AEDF16EE2D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1BFB89CA-83B3-46A1-8B5E-65CBFF7AA361}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1BFB89CA-83B3-46A1-8B5E-65CBFF7AA361}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="29">
   <si>
     <t>Gonzalez Nunez Milton Misael</t>
   </si>
@@ -44,27 +44,15 @@
     <t>Mayra</t>
   </si>
   <si>
-    <t>KDF11</t>
-  </si>
-  <si>
     <t>Ramirez Alvarado Fernando</t>
   </si>
   <si>
-    <t>KDF07/KDF09</t>
-  </si>
-  <si>
     <t>Vela Torres Juan Eduardo</t>
   </si>
   <si>
-    <t>KDF08</t>
-  </si>
-  <si>
     <t>Rodriguez Cabrera Jose Raul</t>
   </si>
   <si>
-    <t>KDF10</t>
-  </si>
-  <si>
     <t>Bautista Martinez Marco Antonio</t>
   </si>
   <si>
@@ -83,9 +71,6 @@
     <t>Pedro</t>
   </si>
   <si>
-    <t>AUX</t>
-  </si>
-  <si>
     <t>Mejia Plascencia Leonardo Rafael</t>
   </si>
   <si>
@@ -101,9 +86,6 @@
     <t>Solorzano De la Cruz Nicolas</t>
   </si>
   <si>
-    <t>KDF17</t>
-  </si>
-  <si>
     <t>Dominguez Macias Guadalupe Monserrat</t>
   </si>
   <si>
@@ -131,9 +113,6 @@
     <t>Omar Barajas</t>
   </si>
   <si>
-    <t>Tecnico</t>
-  </si>
-  <si>
     <t>Farias Julio Cesar</t>
   </si>
   <si>
@@ -144,12 +123,6 @@
   </si>
   <si>
     <t>Nombre</t>
-  </si>
-  <si>
-    <t>Columna1</t>
-  </si>
-  <si>
-    <t>KDF</t>
   </si>
 </sst>
 </file>
@@ -241,7 +214,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -557,274 +530,198 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{062DBA6F-4489-4DE7-907D-35CF6EE6C6E6}">
-  <dimension ref="A1:C25"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="34.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="2"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2" t="s">
+      <c r="B9" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
+      <c r="B10" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B11" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="B12" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="2" t="s">
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="2"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="1" t="s">
+      <c r="B19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
+      <c r="B20" s="1"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
+      <c r="B21" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
+      <c r="B22" s="1"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
+      <c r="B23" s="2"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="2" t="s">
+      <c r="B24" s="1"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>1</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
